--- a/05_Mitochondria/03_complex_subunits/c_data/03_complex_subunits.xlsx
+++ b/05_Mitochondria/03_complex_subunits/c_data/03_complex_subunits.xlsx
@@ -7,8 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="overview" sheetId="1" r:id="rId1"/>
-    <sheet name="subunits" sheetId="2" r:id="rId2"/>
+    <sheet name="subunits" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -352,48 +351,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>sheet</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>subunits</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>131</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Measured subunits and assembly factors of complexes I to V: training logFC and BH FDR per leg, and the interaction (BFR minus HLRT) from the stage 02 fit.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/05_Mitochondria/03_complex_subunits/c_data/03_complex_subunits.xlsx
+++ b/05_Mitochondria/03_complex_subunits/c_data/03_complex_subunits.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -419,31 +419,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NDUFAF4</t>
+          <t>TMEM70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Q9P032</t>
+          <t>Q9BUB7</t>
         </is>
       </c>
       <c r="E2">
-        <v>0.3787258301635852</v>
+        <v>0.4589218076571271</v>
       </c>
       <c r="F2">
-        <v>0.2650915947456821</v>
+        <v>0.1614212077231257</v>
       </c>
       <c r="G2">
-        <v>0.2041161360010477</v>
+        <v>0.2108441029273003</v>
       </c>
       <c r="H2">
-        <v>0.6110841521230971</v>
+        <v>0.5442291452548023</v>
       </c>
       <c r="I2">
-        <v>0.1746096941625375</v>
+        <v>0.2480777047298268</v>
       </c>
       <c r="J2">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="3">
@@ -459,31 +459,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DMAC1</t>
+          <t>NDUFAF4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Q96GE9</t>
+          <t>Q9P032</t>
         </is>
       </c>
       <c r="E3">
-        <v>0.1481436312347846</v>
+        <v>0.4685007426461318</v>
       </c>
       <c r="F3">
-        <v>0.6460043623875977</v>
+        <v>0.1223192727269067</v>
       </c>
       <c r="G3">
-        <v>0.02030201012046362</v>
+        <v>0.2930293895259766</v>
       </c>
       <c r="H3">
-        <v>0.9711568546819457</v>
+        <v>0.333624242744445</v>
       </c>
       <c r="I3">
-        <v>0.127841621114321</v>
+        <v>0.1754713531201553</v>
       </c>
       <c r="J3">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="4">
@@ -499,31 +499,31 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TMEM70</t>
+          <t>DMAC1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q9BUB7</t>
+          <t>Q96GE9</t>
         </is>
       </c>
       <c r="E4">
-        <v>0.3073989004417363</v>
+        <v>0.1664673128833662</v>
       </c>
       <c r="F4">
-        <v>0.5081921954057165</v>
+        <v>0.5772052198128504</v>
       </c>
       <c r="G4">
-        <v>0.2314208215629137</v>
+        <v>0.05029882059801238</v>
       </c>
       <c r="H4">
-        <v>0.6381040614428798</v>
+        <v>0.8744036438605935</v>
       </c>
       <c r="I4">
-        <v>0.07597807887882269</v>
+        <v>0.1161684922853539</v>
       </c>
       <c r="J4">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="5">
@@ -539,31 +539,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NDUFAF3</t>
+          <t>TIMMDC1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q9BU61</t>
+          <t>Q9NPL8</t>
         </is>
       </c>
       <c r="E5">
-        <v>0.254371716819854</v>
+        <v>0.01387840712790833</v>
       </c>
       <c r="F5">
-        <v>0.5478819546025316</v>
+        <v>0.9750839371485145</v>
       </c>
       <c r="G5">
-        <v>0.197071955301638</v>
+        <v>-0.03846674048756249</v>
       </c>
       <c r="H5">
-        <v>0.6552770326898938</v>
+        <v>0.9019197912604475</v>
       </c>
       <c r="I5">
-        <v>0.05729976151821603</v>
+        <v>0.05234514761547082</v>
       </c>
       <c r="J5">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="6">
@@ -579,31 +579,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NUBPL</t>
+          <t>NDUFAF3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q8TB37</t>
+          <t>Q9BU61</t>
         </is>
       </c>
       <c r="E6">
-        <v>0.03760679246592957</v>
+        <v>0.2851672117566935</v>
       </c>
       <c r="F6">
-        <v>0.9553636472623461</v>
+        <v>0.440585012132078</v>
       </c>
       <c r="G6">
-        <v>0.01271099456067049</v>
+        <v>0.2382876618971714</v>
       </c>
       <c r="H6">
-        <v>0.9888687715284962</v>
+        <v>0.4518262543583459</v>
       </c>
       <c r="I6">
-        <v>0.02489579790525909</v>
+        <v>0.04687954985952203</v>
       </c>
       <c r="J6">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="7">
@@ -619,31 +619,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TIMMDC1</t>
+          <t>NUBPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q9NPL8</t>
+          <t>Q8TB37</t>
         </is>
       </c>
       <c r="E7">
-        <v>0.005188272849215636</v>
+        <v>-0.01914760260605064</v>
       </c>
       <c r="F7">
-        <v>0.9905166431939192</v>
+        <v>0.9778477183943963</v>
       </c>
       <c r="G7">
-        <v>0.01899584172950242</v>
+        <v>-0.02962716077414029</v>
       </c>
       <c r="H7">
-        <v>0.9711568546819457</v>
+        <v>0.9582220998512945</v>
       </c>
       <c r="I7">
-        <v>-0.01380756888028678</v>
+        <v>0.01047955816808965</v>
       </c>
       <c r="J7">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="8">
@@ -659,31 +659,31 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AIFM1</t>
+          <t>NDUFAF1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>O95831</t>
+          <t>Q9Y375</t>
         </is>
       </c>
       <c r="E8">
-        <v>0.09234212413252507</v>
+        <v>0.04527327197571829</v>
       </c>
       <c r="F8">
-        <v>0.5133602476710976</v>
+        <v>0.8384254141628561</v>
       </c>
       <c r="G8">
-        <v>0.1495977629401715</v>
+        <v>0.03685186251286332</v>
       </c>
       <c r="H8">
-        <v>0.1828443134705363</v>
+        <v>0.8529895060794223</v>
       </c>
       <c r="I8">
-        <v>-0.05725563880764639</v>
+        <v>0.008421409462854967</v>
       </c>
       <c r="J8">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="9">
@@ -699,31 +699,31 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NDUFAF1</t>
+          <t>AIFM1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Q9Y375</t>
+          <t>O95831</t>
         </is>
       </c>
       <c r="E9">
-        <v>0.01486910829320642</v>
+        <v>0.09761246258211642</v>
       </c>
       <c r="F9">
-        <v>0.9603774702870141</v>
+        <v>0.4744059810283122</v>
       </c>
       <c r="G9">
-        <v>0.07561420499759208</v>
+        <v>0.1395583142618726</v>
       </c>
       <c r="H9">
-        <v>0.7382707626026156</v>
+        <v>0.1606343902863813</v>
       </c>
       <c r="I9">
-        <v>-0.06074509670438566</v>
+        <v>-0.04194585167975617</v>
       </c>
       <c r="J9">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="10">
@@ -739,31 +739,31 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NDUFAF2</t>
+          <t>NDUFAF6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q8N183</t>
+          <t>Q330K2</t>
         </is>
       </c>
       <c r="E10">
-        <v>0.1815284062951292</v>
+        <v>-0.1280852029220547</v>
       </c>
       <c r="F10">
-        <v>0.3595422681009383</v>
+        <v>0.7991555121717145</v>
       </c>
       <c r="G10">
-        <v>0.2437537483657195</v>
+        <v>-0.0427199959859621</v>
       </c>
       <c r="H10">
-        <v>0.1422031707583559</v>
+        <v>0.9314217031416714</v>
       </c>
       <c r="I10">
-        <v>-0.06222534207059027</v>
+        <v>-0.08536520693609262</v>
       </c>
       <c r="J10">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="11">
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="E11">
-        <v>0.2510912561366396</v>
+        <v>0.2450844160815961</v>
       </c>
       <c r="F11">
-        <v>0.2414731952478449</v>
+        <v>0.2907831006381331</v>
       </c>
       <c r="G11">
-        <v>0.3470036387567461</v>
+        <v>0.3679923657946986</v>
       </c>
       <c r="H11">
-        <v>0.05746083750890202</v>
+        <v>0.03996341642837331</v>
       </c>
       <c r="I11">
-        <v>-0.09591238262010648</v>
+        <v>-0.1229079497131025</v>
       </c>
       <c r="J11">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="12">
@@ -819,31 +819,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NDUFAF5</t>
+          <t>NDUFAF2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Q5TEU4</t>
+          <t>Q8N183</t>
         </is>
       </c>
       <c r="E12">
-        <v>0.01529529510791505</v>
+        <v>0.112109582659393</v>
       </c>
       <c r="F12">
-        <v>0.9826070070796277</v>
+        <v>0.6287686430851547</v>
       </c>
       <c r="G12">
-        <v>0.1291675214345851</v>
+        <v>0.2468357440374547</v>
       </c>
       <c r="H12">
-        <v>0.7856203741320924</v>
+        <v>0.1000040877355797</v>
       </c>
       <c r="I12">
-        <v>-0.11387222632667</v>
+        <v>-0.1347261613780617</v>
       </c>
       <c r="J12">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="13">
@@ -859,31 +859,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NDUFAF6</t>
+          <t>NDUFAF7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Q330K2</t>
+          <t>Q7L592</t>
         </is>
       </c>
       <c r="E13">
-        <v>-0.1751375517228126</v>
+        <v>-0.05948774663816714</v>
       </c>
       <c r="F13">
-        <v>0.6755165576158051</v>
+        <v>0.854568844579095</v>
       </c>
       <c r="G13">
-        <v>-0.05604624988438545</v>
+        <v>0.08934003378114319</v>
       </c>
       <c r="H13">
-        <v>0.927644255344944</v>
+        <v>0.7017884802061151</v>
       </c>
       <c r="I13">
-        <v>-0.1190913018384272</v>
+        <v>-0.1488277804193103</v>
       </c>
       <c r="J13">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="14">
@@ -899,31 +899,31 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NDUFAF7</t>
+          <t>NDUFAF5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Q7L592</t>
+          <t>Q5TEU4</t>
         </is>
       </c>
       <c r="E14">
-        <v>-0.0413249514884928</v>
+        <v>-0.05920427096711833</v>
       </c>
       <c r="F14">
-        <v>0.9192074786220314</v>
+        <v>0.9058032063172038</v>
       </c>
       <c r="G14">
-        <v>0.1704235679815174</v>
+        <v>0.2120321301047383</v>
       </c>
       <c r="H14">
-        <v>0.5884369935881379</v>
+        <v>0.4938847459881079</v>
       </c>
       <c r="I14">
-        <v>-0.2117485194700102</v>
+        <v>-0.2712364010718566</v>
       </c>
       <c r="J14">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="15">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="E15">
-        <v>0.01259050625816727</v>
+        <v>-0.03917343613179725</v>
       </c>
       <c r="F15">
-        <v>0.9845027801946095</v>
+        <v>0.9399464246056088</v>
       </c>
       <c r="G15">
-        <v>0.3124885290698991</v>
+        <v>0.4613404695858208</v>
       </c>
       <c r="H15">
-        <v>0.3358156292392915</v>
+        <v>0.06190390212672413</v>
       </c>
       <c r="I15">
-        <v>-0.2998980228117318</v>
+        <v>-0.500513905717618</v>
       </c>
       <c r="J15">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="16">
@@ -988,22 +988,22 @@
         </is>
       </c>
       <c r="E16">
-        <v>0.4235523316967225</v>
+        <v>0.3971709756980069</v>
       </c>
       <c r="F16">
-        <v>0.1404786328119245</v>
+        <v>0.1462911164237576</v>
       </c>
       <c r="G16">
-        <v>-0.003484061569388075</v>
+        <v>0.0936219220088681</v>
       </c>
       <c r="H16">
-        <v>0.9972952269581049</v>
+        <v>0.7816842508192055</v>
       </c>
       <c r="I16">
-        <v>0.4270363932661105</v>
+        <v>0.3035490536891388</v>
       </c>
       <c r="J16">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="17">
@@ -1028,22 +1028,22 @@
         </is>
       </c>
       <c r="E17">
-        <v>0.09229242636346413</v>
+        <v>0.1953384747810247</v>
       </c>
       <c r="F17">
-        <v>0.8070861154188188</v>
+        <v>0.5317253736073706</v>
       </c>
       <c r="G17">
-        <v>-0.0415490296239085</v>
+        <v>-0.06632465076875604</v>
       </c>
       <c r="H17">
-        <v>0.9380728197870072</v>
+        <v>0.8423088459926701</v>
       </c>
       <c r="I17">
-        <v>0.1338414559873726</v>
+        <v>0.2616631255497808</v>
       </c>
       <c r="J17">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="18">
@@ -1059,31 +1059,31 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MT-ND5</t>
+          <t>MT-ND2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P03915</t>
+          <t>P03891</t>
         </is>
       </c>
       <c r="E18">
-        <v>0.1411365816750347</v>
+        <v>0.2976824323721026</v>
       </c>
       <c r="F18">
-        <v>0.6482144393958151</v>
+        <v>0.4741225737179004</v>
       </c>
       <c r="G18">
-        <v>0.008981288389321662</v>
+        <v>0.06696769245645839</v>
       </c>
       <c r="H18">
-        <v>0.9880321577292903</v>
+        <v>0.8934322547448574</v>
       </c>
       <c r="I18">
-        <v>0.1321552932857131</v>
+        <v>0.2307147399156442</v>
       </c>
       <c r="J18">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="19">
@@ -1099,31 +1099,31 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MT-ND3</t>
+          <t>MT-ND5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P03897</t>
+          <t>P03915</t>
         </is>
       </c>
       <c r="E19">
-        <v>0.09360636290398361</v>
+        <v>0.1912953651984921</v>
       </c>
       <c r="F19">
-        <v>0.7104466430469145</v>
+        <v>0.468377567541768</v>
       </c>
       <c r="G19">
-        <v>0.01643467113115804</v>
+        <v>0.02797384447844919</v>
       </c>
       <c r="H19">
-        <v>0.9689262900471275</v>
+        <v>0.9314217031416714</v>
       </c>
       <c r="I19">
-        <v>0.07717169177282557</v>
+        <v>0.1633215207200429</v>
       </c>
       <c r="J19">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="20">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="E20">
-        <v>0.069897407631899</v>
+        <v>0.04381227297241708</v>
       </c>
       <c r="F20">
-        <v>0.8805508448520581</v>
+        <v>0.9357278002470788</v>
       </c>
       <c r="G20">
-        <v>0.01859992026695068</v>
+        <v>-0.1036968171743133</v>
       </c>
       <c r="H20">
-        <v>0.9795401145666757</v>
+        <v>0.7845851148134271</v>
       </c>
       <c r="I20">
-        <v>0.05129748736494832</v>
+        <v>0.1475090901467304</v>
       </c>
       <c r="J20">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="21">
@@ -1179,31 +1179,31 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NDUFA3</t>
+          <t>MT-ND3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>O95167</t>
+          <t>P03897</t>
         </is>
       </c>
       <c r="E21">
-        <v>0.07140276059880435</v>
+        <v>0.1876492408978407</v>
       </c>
       <c r="F21">
-        <v>0.9008277534056409</v>
+        <v>0.346605165775334</v>
       </c>
       <c r="G21">
-        <v>0.02062250822897127</v>
+        <v>0.04081553808711647</v>
       </c>
       <c r="H21">
-        <v>0.9822554032206443</v>
+        <v>0.8671863390372599</v>
       </c>
       <c r="I21">
-        <v>0.05078025236983308</v>
+        <v>0.1468337028107243</v>
       </c>
       <c r="J21">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="22">
@@ -1228,22 +1228,22 @@
         </is>
       </c>
       <c r="E22">
-        <v>0.1708834117173055</v>
+        <v>0.173071334118351</v>
       </c>
       <c r="F22">
-        <v>0.5813889103984707</v>
+        <v>0.5443788131327548</v>
       </c>
       <c r="G22">
-        <v>0.1583811502243826</v>
+        <v>0.09688433336228996</v>
       </c>
       <c r="H22">
-        <v>0.6031590315609475</v>
+        <v>0.7003148851759506</v>
       </c>
       <c r="I22">
-        <v>0.01250226149292288</v>
+        <v>0.076187000756061</v>
       </c>
       <c r="J22">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="23">
@@ -1259,31 +1259,31 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MT-ND2</t>
+          <t>MT-ND1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P03891</t>
+          <t>P03886</t>
         </is>
       </c>
       <c r="E23">
-        <v>0.1266602157383545</v>
+        <v>0.1750093895604579</v>
       </c>
       <c r="F23">
-        <v>0.7760591778093494</v>
+        <v>0.7021179587481993</v>
       </c>
       <c r="G23">
-        <v>0.1147772431632887</v>
+        <v>0.1652027019897027</v>
       </c>
       <c r="H23">
-        <v>0.8341476079486612</v>
+        <v>0.6447688140358171</v>
       </c>
       <c r="I23">
-        <v>0.01188297257506576</v>
+        <v>0.009806687570755201</v>
       </c>
       <c r="J23">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="24">
@@ -1299,31 +1299,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NDUFB11</t>
+          <t>NDUFS4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Q9NX14</t>
+          <t>O43181</t>
         </is>
       </c>
       <c r="E24">
-        <v>0.1295569506995271</v>
+        <v>0.1169293732288992</v>
       </c>
       <c r="F24">
-        <v>0.5959132176399329</v>
+        <v>0.6806426822406901</v>
       </c>
       <c r="G24">
-        <v>0.1283287540769251</v>
+        <v>0.1168144275050444</v>
       </c>
       <c r="H24">
-        <v>0.5874816365106807</v>
+        <v>0.6086787459674382</v>
       </c>
       <c r="I24">
-        <v>0.001228196622601985</v>
+        <v>0.0001149457238547313</v>
       </c>
       <c r="J24">
-        <v>0.9999092528331825</v>
+        <v>0.9994246244385309</v>
       </c>
     </row>
     <row r="25">
@@ -1339,31 +1339,31 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NDUFS4</t>
+          <t>NDUFA9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>O43181</t>
+          <t>Q16795</t>
         </is>
       </c>
       <c r="E25">
-        <v>0.144075213518029</v>
+        <v>0.1613254821311791</v>
       </c>
       <c r="F25">
-        <v>0.5979927475415191</v>
+        <v>0.4770152216342594</v>
       </c>
       <c r="G25">
-        <v>0.1682148862951145</v>
+        <v>0.1687131604230956</v>
       </c>
       <c r="H25">
-        <v>0.5060400039901967</v>
+        <v>0.3560560498377239</v>
       </c>
       <c r="I25">
-        <v>-0.02413967277708551</v>
+        <v>-0.007387678291916444</v>
       </c>
       <c r="J25">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="26">
@@ -1379,31 +1379,31 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NDUFB8</t>
+          <t>MT-ND4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>O95169</t>
+          <t>P03905</t>
         </is>
       </c>
       <c r="E26">
-        <v>0.1448518571365334</v>
+        <v>0.1258765167094573</v>
       </c>
       <c r="F26">
-        <v>0.7186287582391777</v>
+        <v>0.8033974278342424</v>
       </c>
       <c r="G26">
-        <v>0.1847241093681333</v>
+        <v>0.1391436184563588</v>
       </c>
       <c r="H26">
-        <v>0.624814517285457</v>
+        <v>0.7155001829061558</v>
       </c>
       <c r="I26">
-        <v>-0.03987225223159996</v>
+        <v>-0.01326710174690149</v>
       </c>
       <c r="J26">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="27">
@@ -1419,31 +1419,31 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NDUFA9</t>
+          <t>NDUFS5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Q16795</t>
+          <t>O43920</t>
         </is>
       </c>
       <c r="E27">
-        <v>0.1519393472401021</v>
+        <v>0.05623191404147931</v>
       </c>
       <c r="F27">
-        <v>0.548353087490032</v>
+        <v>0.8223943596164377</v>
       </c>
       <c r="G27">
-        <v>0.1926011646672983</v>
+        <v>0.07365068422369703</v>
       </c>
       <c r="H27">
-        <v>0.391982032419309</v>
+        <v>0.6853701129714189</v>
       </c>
       <c r="I27">
-        <v>-0.04066181742719621</v>
+        <v>-0.01741877018221771</v>
       </c>
       <c r="J27">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="28">
@@ -1459,31 +1459,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NDUFS5</t>
+          <t>NDUFV1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>O43920</t>
+          <t>P49821</t>
         </is>
       </c>
       <c r="E28">
-        <v>0.05687937822496281</v>
+        <v>0.1215421194898525</v>
       </c>
       <c r="F28">
-        <v>0.7994174287640302</v>
+        <v>0.4770152216342594</v>
       </c>
       <c r="G28">
-        <v>0.09923885808240129</v>
+        <v>0.1497884831809628</v>
       </c>
       <c r="H28">
-        <v>0.6421291394239836</v>
+        <v>0.2579214254814539</v>
       </c>
       <c r="I28">
-        <v>-0.04235947985743849</v>
+        <v>-0.02824636369111033</v>
       </c>
       <c r="J28">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="29">
@@ -1499,31 +1499,31 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NDUFV1</t>
+          <t>NDUFA3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P49821</t>
+          <t>O95167</t>
         </is>
       </c>
       <c r="E29">
-        <v>0.116614163549837</v>
+        <v>-0.01328596017341255</v>
       </c>
       <c r="F29">
-        <v>0.5442548591265827</v>
+        <v>0.9853325286010158</v>
       </c>
       <c r="G29">
-        <v>0.1633758823087419</v>
+        <v>0.01556176592934122</v>
       </c>
       <c r="H29">
-        <v>0.3003491383025697</v>
+        <v>0.9809985037563523</v>
       </c>
       <c r="I29">
-        <v>-0.04676171875890489</v>
+        <v>-0.02884772610275377</v>
       </c>
       <c r="J29">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="30">
@@ -1539,31 +1539,31 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NDUFB10</t>
+          <t>NDUFB8</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>O96000</t>
+          <t>O95169</t>
         </is>
       </c>
       <c r="E30">
-        <v>0.1499298692502364</v>
+        <v>0.1335801729299853</v>
       </c>
       <c r="F30">
-        <v>0.506835859459293</v>
+        <v>0.7367292501295457</v>
       </c>
       <c r="G30">
-        <v>0.1982283787998327</v>
+        <v>0.170065085947801</v>
       </c>
       <c r="H30">
-        <v>0.2993739856935353</v>
+        <v>0.5670404022135267</v>
       </c>
       <c r="I30">
-        <v>-0.04829850954959625</v>
+        <v>-0.03648491301781576</v>
       </c>
       <c r="J30">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="31">
@@ -1579,31 +1579,31 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NDUFAB1</t>
+          <t>NDUFB11</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>O14561</t>
+          <t>Q9NX14</t>
         </is>
       </c>
       <c r="E31">
-        <v>0.08749699891676244</v>
+        <v>0.1063034550302326</v>
       </c>
       <c r="F31">
-        <v>0.8113315488436527</v>
+        <v>0.6609031295045805</v>
       </c>
       <c r="G31">
-        <v>0.1536241590355303</v>
+        <v>0.158074103140919</v>
       </c>
       <c r="H31">
-        <v>0.6552770326898938</v>
+        <v>0.3609449874067917</v>
       </c>
       <c r="I31">
-        <v>-0.06612716011876785</v>
+        <v>-0.05177064811068632</v>
       </c>
       <c r="J31">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="32">
@@ -1628,22 +1628,22 @@
         </is>
       </c>
       <c r="E32">
-        <v>0.1545152254356417</v>
+        <v>0.1423091974754342</v>
       </c>
       <c r="F32">
-        <v>0.350426217365032</v>
+        <v>0.3181382362231954</v>
       </c>
       <c r="G32">
-        <v>0.2234109210606405</v>
+        <v>0.1980841242612819</v>
       </c>
       <c r="H32">
-        <v>0.09667671505212558</v>
+        <v>0.0663146381882026</v>
       </c>
       <c r="I32">
-        <v>-0.06889569562499887</v>
+        <v>-0.05577492678584761</v>
       </c>
       <c r="J32">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="33">
@@ -1659,31 +1659,31 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NDUFS6</t>
+          <t>NDUFA1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>O75380</t>
+          <t>O15239</t>
         </is>
       </c>
       <c r="E33">
-        <v>0.1434634197684197</v>
+        <v>-0.1152679421103997</v>
       </c>
       <c r="F33">
-        <v>0.548353087490032</v>
+        <v>0.8223943596164377</v>
       </c>
       <c r="G33">
-        <v>0.2216567823028299</v>
+        <v>-0.04426185951477279</v>
       </c>
       <c r="H33">
-        <v>0.2613725296735063</v>
+        <v>0.9290575553721193</v>
       </c>
       <c r="I33">
-        <v>-0.07819336253441023</v>
+        <v>-0.07100608259562691</v>
       </c>
       <c r="J33">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="34">
@@ -1699,31 +1699,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MT-ND1</t>
+          <t>NDUFB10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P03886</t>
+          <t>O96000</t>
         </is>
       </c>
       <c r="E34">
-        <v>0.1025876999286339</v>
+        <v>0.1414882687791739</v>
       </c>
       <c r="F34">
-        <v>0.8269590647110925</v>
+        <v>0.4913855309108684</v>
       </c>
       <c r="G34">
-        <v>0.1923807362852727</v>
+        <v>0.215888473277154</v>
       </c>
       <c r="H34">
-        <v>0.6662175445549882</v>
+        <v>0.1492550892143182</v>
       </c>
       <c r="I34">
-        <v>-0.08979303635663882</v>
+        <v>-0.07440020449798013</v>
       </c>
       <c r="J34">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="35">
@@ -1739,31 +1739,31 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NDUFB1</t>
+          <t>NDUFS7</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>O75438</t>
+          <t>O75251</t>
         </is>
       </c>
       <c r="E35">
-        <v>0.07793586079539594</v>
+        <v>0.08273684613260812</v>
       </c>
       <c r="F35">
-        <v>0.8018373115114885</v>
+        <v>0.7678002281358539</v>
       </c>
       <c r="G35">
-        <v>0.1700008890217006</v>
+        <v>0.1638047047452353</v>
       </c>
       <c r="H35">
-        <v>0.5442651746864123</v>
+        <v>0.3942191375176417</v>
       </c>
       <c r="I35">
-        <v>-0.09206502822630469</v>
+        <v>-0.08106785861262722</v>
       </c>
       <c r="J35">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="36">
@@ -1779,31 +1779,31 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NDUFA13</t>
+          <t>NDUFB3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Q9P0J0</t>
+          <t>O43676</t>
         </is>
       </c>
       <c r="E36">
-        <v>0.0455904413405932</v>
+        <v>0.02734110168796988</v>
       </c>
       <c r="F36">
-        <v>0.909335573699129</v>
+        <v>0.9454340982644854</v>
       </c>
       <c r="G36">
-        <v>0.1382997820670155</v>
+        <v>0.1084629464482951</v>
       </c>
       <c r="H36">
-        <v>0.6796027823086476</v>
+        <v>0.6544027785462442</v>
       </c>
       <c r="I36">
-        <v>-0.09270934072642234</v>
+        <v>-0.08112184476032525</v>
       </c>
       <c r="J36">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="37">
@@ -1819,31 +1819,31 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NDUFA12</t>
+          <t>NDUFA5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Q9UI09</t>
+          <t>Q16718</t>
         </is>
       </c>
       <c r="E37">
-        <v>0.07471812025159252</v>
+        <v>-0.04676687886195552</v>
       </c>
       <c r="F37">
-        <v>0.7709504666491616</v>
+        <v>0.8696132789890926</v>
       </c>
       <c r="G37">
-        <v>0.1734428147131091</v>
+        <v>0.03455919264096963</v>
       </c>
       <c r="H37">
-        <v>0.4171382471615974</v>
+        <v>0.8933548174740757</v>
       </c>
       <c r="I37">
-        <v>-0.09872469446151655</v>
+        <v>-0.08132607150292515</v>
       </c>
       <c r="J37">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="38">
@@ -1859,31 +1859,31 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NDUFB9</t>
+          <t>NDUFA10</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Q9Y6M9</t>
+          <t>O95299</t>
         </is>
       </c>
       <c r="E38">
-        <v>0.1079647481159469</v>
+        <v>0.07378657590094662</v>
       </c>
       <c r="F38">
-        <v>0.6909047476815349</v>
+        <v>0.7292035365183294</v>
       </c>
       <c r="G38">
-        <v>0.213209367349549</v>
+        <v>0.1561331273248605</v>
       </c>
       <c r="H38">
-        <v>0.3148536870860472</v>
+        <v>0.2601131055343209</v>
       </c>
       <c r="I38">
-        <v>-0.1052446192336021</v>
+        <v>-0.08234655142391389</v>
       </c>
       <c r="J38">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="39">
@@ -1899,31 +1899,31 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NDUFV2</t>
+          <t>NDUFB1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>P19404</t>
+          <t>O75438</t>
         </is>
       </c>
       <c r="E39">
-        <v>0.1250271696216423</v>
+        <v>0.054019219422905</v>
       </c>
       <c r="F39">
-        <v>0.5618300791770688</v>
+        <v>0.8894907477548268</v>
       </c>
       <c r="G39">
-        <v>0.2342498850672712</v>
+        <v>0.1516904949892499</v>
       </c>
       <c r="H39">
-        <v>0.1484225376570935</v>
+        <v>0.5393765769438398</v>
       </c>
       <c r="I39">
-        <v>-0.1092227154456289</v>
+        <v>-0.09767127556634492</v>
       </c>
       <c r="J39">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="40">
@@ -1939,31 +1939,31 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NDUFA5</t>
+          <t>NDUFAB1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Q16718</t>
+          <t>O14561</t>
         </is>
       </c>
       <c r="E40">
-        <v>-0.004422801139366328</v>
+        <v>0.07494536412998087</v>
       </c>
       <c r="F40">
-        <v>0.9900334099762556</v>
+        <v>0.8513438503192678</v>
       </c>
       <c r="G40">
-        <v>0.1074984457131407</v>
+        <v>0.1788450362121559</v>
       </c>
       <c r="H40">
-        <v>0.6662175445549882</v>
+        <v>0.4778822415805428</v>
       </c>
       <c r="I40">
-        <v>-0.111921246852507</v>
+        <v>-0.103899672082175</v>
       </c>
       <c r="J40">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="41">
@@ -1979,31 +1979,31 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NDUFC2</t>
+          <t>NDUFA8</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>O95298</t>
+          <t>P51970</t>
         </is>
       </c>
       <c r="E41">
-        <v>0.1659038455320427</v>
+        <v>0.059825702953475</v>
       </c>
       <c r="F41">
-        <v>0.6889900321421828</v>
+        <v>0.8519334801678393</v>
       </c>
       <c r="G41">
-        <v>0.2929384004028108</v>
+        <v>0.17484489948502</v>
       </c>
       <c r="H41">
-        <v>0.4012222374863637</v>
+        <v>0.3689090642151751</v>
       </c>
       <c r="I41">
-        <v>-0.1270345548707681</v>
+        <v>-0.115019196531545</v>
       </c>
       <c r="J41">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="42">
@@ -2019,31 +2019,31 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NDUFB3</t>
+          <t>NDUFS6</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>O43676</t>
+          <t>O75380</t>
         </is>
       </c>
       <c r="E42">
-        <v>-0.0009677538371626326</v>
+        <v>0.1073763407068924</v>
       </c>
       <c r="F42">
-        <v>0.9967734640645376</v>
+        <v>0.6466671522554328</v>
       </c>
       <c r="G42">
-        <v>0.1327703936890501</v>
+        <v>0.2233385878092733</v>
       </c>
       <c r="H42">
-        <v>0.6686143882399689</v>
+        <v>0.1510637374688628</v>
       </c>
       <c r="I42">
-        <v>-0.1337381475262127</v>
+        <v>-0.1159622471023809</v>
       </c>
       <c r="J42">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="43">
@@ -2059,31 +2059,31 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NDUFA1</t>
+          <t>NDUFA12</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>O15239</t>
+          <t>Q9UI09</t>
         </is>
       </c>
       <c r="E43">
-        <v>-0.1166757361717803</v>
+        <v>0.05903711755233232</v>
       </c>
       <c r="F43">
-        <v>0.8296268838574398</v>
+        <v>0.825131047611213</v>
       </c>
       <c r="G43">
-        <v>0.01746559698029948</v>
+        <v>0.1772871159159308</v>
       </c>
       <c r="H43">
-        <v>0.9872331897787912</v>
+        <v>0.2868549893703825</v>
       </c>
       <c r="I43">
-        <v>-0.1341413331520798</v>
+        <v>-0.1182499983635985</v>
       </c>
       <c r="J43">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="44">
@@ -2099,31 +2099,31 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NDUFA10</t>
+          <t>NDUFV2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>O95299</t>
+          <t>P19404</t>
         </is>
       </c>
       <c r="E44">
-        <v>0.05149787420618779</v>
+        <v>0.123295531468532</v>
       </c>
       <c r="F44">
-        <v>0.8154133021922859</v>
+        <v>0.524173289694625</v>
       </c>
       <c r="G44">
-        <v>0.1864014416786794</v>
+        <v>0.2428361099026262</v>
       </c>
       <c r="H44">
-        <v>0.2531855477336942</v>
+        <v>0.06178349166883927</v>
       </c>
       <c r="I44">
-        <v>-0.1349035674724917</v>
+        <v>-0.1195405784340942</v>
       </c>
       <c r="J44">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="45">
@@ -2139,31 +2139,31 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NDUFB4</t>
+          <t>NDUFA13</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>O95168</t>
+          <t>Q9P0J0</t>
         </is>
       </c>
       <c r="E45">
-        <v>0.1180828463263062</v>
+        <v>0.02529928978005458</v>
       </c>
       <c r="F45">
-        <v>0.7285925743122293</v>
+        <v>0.9512434668216292</v>
       </c>
       <c r="G45">
-        <v>0.2539602065261306</v>
+        <v>0.149039120935953</v>
       </c>
       <c r="H45">
-        <v>0.3658924518899666</v>
+        <v>0.5200141853579404</v>
       </c>
       <c r="I45">
-        <v>-0.1358773601998244</v>
+        <v>-0.1237398311558984</v>
       </c>
       <c r="J45">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="46">
@@ -2179,31 +2179,31 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MT-ND4</t>
+          <t>NDUFB7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P03905</t>
+          <t>P17568</t>
         </is>
       </c>
       <c r="E46">
-        <v>0.01418423251540446</v>
+        <v>0.1435052146835751</v>
       </c>
       <c r="F46">
-        <v>0.984556569584754</v>
+        <v>0.6020496903570424</v>
       </c>
       <c r="G46">
-        <v>0.1558833301730012</v>
+        <v>0.2746862580534639</v>
       </c>
       <c r="H46">
-        <v>0.7695776447727801</v>
+        <v>0.1376337318910182</v>
       </c>
       <c r="I46">
-        <v>-0.1416990976575967</v>
+        <v>-0.1311810433698888</v>
       </c>
       <c r="J46">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="47">
@@ -2219,31 +2219,31 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NDUFB7</t>
+          <t>NDUFB4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P17568</t>
+          <t>O95168</t>
         </is>
       </c>
       <c r="E47">
-        <v>0.1297598080550912</v>
+        <v>0.1072557504191067</v>
       </c>
       <c r="F47">
-        <v>0.6655234535014396</v>
+        <v>0.7717266552891399</v>
       </c>
       <c r="G47">
-        <v>0.2762294713983557</v>
+        <v>0.2470342769302434</v>
       </c>
       <c r="H47">
-        <v>0.2339041345855489</v>
+        <v>0.3201546914262107</v>
       </c>
       <c r="I47">
-        <v>-0.1464696633432645</v>
+        <v>-0.1397785265111366</v>
       </c>
       <c r="J47">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="48">
@@ -2259,31 +2259,31 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NDUFS8</t>
+          <t>NDUFB9</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>O00217</t>
+          <t>Q9Y6M9</t>
         </is>
       </c>
       <c r="E48">
-        <v>0.2100835099982454</v>
+        <v>0.09920971499695952</v>
       </c>
       <c r="F48">
-        <v>0.4944324393820637</v>
+        <v>0.7175923838428081</v>
       </c>
       <c r="G48">
-        <v>0.3666826211855216</v>
+        <v>0.2399853449330216</v>
       </c>
       <c r="H48">
-        <v>0.1169462792286606</v>
+        <v>0.1600269011119832</v>
       </c>
       <c r="I48">
-        <v>-0.1565991111872762</v>
+        <v>-0.1407756299360621</v>
       </c>
       <c r="J48">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="49">
@@ -2299,31 +2299,31 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NDUFS7</t>
+          <t>NDUFS8</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>O75251</t>
+          <t>O00217</t>
         </is>
       </c>
       <c r="E49">
-        <v>0.0493215470459667</v>
+        <v>0.1780193888399886</v>
       </c>
       <c r="F49">
-        <v>0.8707592867279107</v>
+        <v>0.5456774277939418</v>
       </c>
       <c r="G49">
-        <v>0.2156490375359432</v>
+        <v>0.3301735974612754</v>
       </c>
       <c r="H49">
-        <v>0.3140076669701554</v>
+        <v>0.09793316201348828</v>
       </c>
       <c r="I49">
-        <v>-0.1663274904899765</v>
+        <v>-0.1521542086212868</v>
       </c>
       <c r="J49">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="50">
@@ -2339,31 +2339,31 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NDUFA8</t>
+          <t>NDUFB6</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P51970</t>
+          <t>O95139</t>
         </is>
       </c>
       <c r="E50">
-        <v>0.06038131703198601</v>
+        <v>0.1089061621215528</v>
       </c>
       <c r="F50">
-        <v>0.8377005505886472</v>
+        <v>0.8223943596164377</v>
       </c>
       <c r="G50">
-        <v>0.2298879785571444</v>
+        <v>0.2725549444839253</v>
       </c>
       <c r="H50">
-        <v>0.2993739856935353</v>
+        <v>0.3725778704137638</v>
       </c>
       <c r="I50">
-        <v>-0.1695066615251584</v>
+        <v>-0.1636487823623725</v>
       </c>
       <c r="J50">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="51">
@@ -2379,31 +2379,31 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NDUFA7</t>
+          <t>NDUFA6</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>O95182</t>
+          <t>P56556</t>
         </is>
       </c>
       <c r="E51">
-        <v>0.01652098804388658</v>
+        <v>0.01918514704765428</v>
       </c>
       <c r="F51">
-        <v>0.9708555534965511</v>
+        <v>0.9688180691436048</v>
       </c>
       <c r="G51">
-        <v>0.1983294670307245</v>
+        <v>0.1874102447156787</v>
       </c>
       <c r="H51">
-        <v>0.4304678380396108</v>
+        <v>0.3957198010268816</v>
       </c>
       <c r="I51">
-        <v>-0.1818084789868379</v>
+        <v>-0.1682250976680244</v>
       </c>
       <c r="J51">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="52">
@@ -2419,31 +2419,31 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NDUFA6</t>
+          <t>NDUFC2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P56556</t>
+          <t>O95298</t>
         </is>
       </c>
       <c r="E52">
-        <v>0.01313669049139676</v>
+        <v>0.1423972313050967</v>
       </c>
       <c r="F52">
-        <v>0.9809746124312042</v>
+        <v>0.7367292501295457</v>
       </c>
       <c r="G52">
-        <v>0.1962647715685897</v>
+        <v>0.3241700775360528</v>
       </c>
       <c r="H52">
-        <v>0.4511583941471301</v>
+        <v>0.2463437372155354</v>
       </c>
       <c r="I52">
-        <v>-0.1831280810771929</v>
+        <v>-0.181772846230956</v>
       </c>
       <c r="J52">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="53">
@@ -2459,31 +2459,31 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NDUFB6</t>
+          <t>NDUFS2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>O95139</t>
+          <t>O75306</t>
         </is>
       </c>
       <c r="E53">
-        <v>0.08574589913556707</v>
+        <v>-0.009995660406129758</v>
       </c>
       <c r="F53">
-        <v>0.8574829013852061</v>
+        <v>0.9778477183943963</v>
       </c>
       <c r="G53">
-        <v>0.2863409058675899</v>
+        <v>0.2094486978879218</v>
       </c>
       <c r="H53">
-        <v>0.441712732675913</v>
+        <v>0.2054233700428175</v>
       </c>
       <c r="I53">
-        <v>-0.2005950067320228</v>
+        <v>-0.2194443582940515</v>
       </c>
       <c r="J53">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="54">
@@ -2499,31 +2499,31 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NDUFV3</t>
+          <t>NDUFB5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P56181</t>
+          <t>O43674</t>
         </is>
       </c>
       <c r="E54">
-        <v>-0.005986281687111017</v>
+        <v>0.1554020630243187</v>
       </c>
       <c r="F54">
-        <v>0.989539060774334</v>
+        <v>0.6686189619875664</v>
       </c>
       <c r="G54">
-        <v>0.204210444411288</v>
+        <v>0.3852892555548841</v>
       </c>
       <c r="H54">
-        <v>0.4388277970199533</v>
+        <v>0.09192237674397873</v>
       </c>
       <c r="I54">
-        <v>-0.210196726098399</v>
+        <v>-0.2298871925305654</v>
       </c>
       <c r="J54">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="55">
@@ -2539,31 +2539,31 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NDUFB5</t>
+          <t>NDUFA7</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>O43674</t>
+          <t>O95182</t>
         </is>
       </c>
       <c r="E55">
-        <v>0.1521124129465541</v>
+        <v>-0.07031844354461825</v>
       </c>
       <c r="F55">
-        <v>0.6762148343709982</v>
+        <v>0.8291083179587776</v>
       </c>
       <c r="G55">
-        <v>0.3627058025242711</v>
+        <v>0.1620634851780025</v>
       </c>
       <c r="H55">
-        <v>0.1815217271415152</v>
+        <v>0.4477688433359416</v>
       </c>
       <c r="I55">
-        <v>-0.210593389577717</v>
+        <v>-0.2323819287226208</v>
       </c>
       <c r="J55">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="56">
@@ -2579,31 +2579,31 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NDUFS2</t>
+          <t>NDUFV3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>O75306</t>
+          <t>P56181</t>
         </is>
       </c>
       <c r="E56">
-        <v>-0.003051563888618603</v>
+        <v>0.002476927707970589</v>
       </c>
       <c r="F56">
-        <v>0.9922796321841778</v>
+        <v>0.9945721009772818</v>
       </c>
       <c r="G56">
-        <v>0.2177637257180933</v>
+        <v>0.2662354312290205</v>
       </c>
       <c r="H56">
-        <v>0.2846167256509129</v>
+        <v>0.1943949650390293</v>
       </c>
       <c r="I56">
-        <v>-0.2208152896067119</v>
+        <v>-0.2637585035210499</v>
       </c>
       <c r="J56">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="57">
@@ -2628,22 +2628,22 @@
         </is>
       </c>
       <c r="E57">
-        <v>0.3774380727169948</v>
+        <v>0.2431736424953517</v>
       </c>
       <c r="F57">
-        <v>0.07644949186152107</v>
+        <v>0.2615555164072635</v>
       </c>
       <c r="G57">
-        <v>-0.01542821662111393</v>
+        <v>-0.01711501715976382</v>
       </c>
       <c r="H57">
-        <v>0.9776798780251716</v>
+        <v>0.9585505812611249</v>
       </c>
       <c r="I57">
-        <v>0.3928662893381087</v>
+        <v>0.2602886596551155</v>
       </c>
       <c r="J57">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="58">
@@ -2668,22 +2668,22 @@
         </is>
       </c>
       <c r="E58">
-        <v>0.3294322371938634</v>
+        <v>0.3710019879060074</v>
       </c>
       <c r="F58">
-        <v>0.5866213655753396</v>
+        <v>0.4025486376136241</v>
       </c>
       <c r="G58">
-        <v>0.1720937737759218</v>
+        <v>0.1681271041222629</v>
       </c>
       <c r="H58">
-        <v>0.8158849946918871</v>
+        <v>0.7017884802061151</v>
       </c>
       <c r="I58">
-        <v>0.1573384634179416</v>
+        <v>0.2028748837837444</v>
       </c>
       <c r="J58">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="59">
@@ -2708,22 +2708,22 @@
         </is>
       </c>
       <c r="E59">
-        <v>0.3201343641594541</v>
+        <v>0.4934631975514563</v>
       </c>
       <c r="F59">
-        <v>0.5821935651738257</v>
+        <v>0.3453783691981687</v>
       </c>
       <c r="G59">
-        <v>0.1415974970716078</v>
+        <v>0.2914516965127945</v>
       </c>
       <c r="H59">
-        <v>0.8539066303618239</v>
+        <v>0.5533761845135268</v>
       </c>
       <c r="I59">
-        <v>0.1785368670878462</v>
+        <v>0.2020115010386618</v>
       </c>
       <c r="J59">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="60">
@@ -2748,22 +2748,22 @@
         </is>
       </c>
       <c r="E60">
-        <v>0.1563873368660644</v>
+        <v>0.3791407693219746</v>
       </c>
       <c r="F60">
-        <v>0.6967167724963367</v>
+        <v>0.2099056253245155</v>
       </c>
       <c r="G60">
-        <v>0.1252558177543612</v>
+        <v>0.184638788000651</v>
       </c>
       <c r="H60">
-        <v>0.7802662831557282</v>
+        <v>0.5502549078715574</v>
       </c>
       <c r="I60">
-        <v>0.0311315191117032</v>
+        <v>0.1945019813213236</v>
       </c>
       <c r="J60">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="61">
@@ -2788,22 +2788,22 @@
         </is>
       </c>
       <c r="E61">
-        <v>0.08959169378188037</v>
+        <v>0.1237678458628899</v>
       </c>
       <c r="F61">
-        <v>0.5866213655753396</v>
+        <v>0.3963652891230159</v>
       </c>
       <c r="G61">
-        <v>0.0856715304492468</v>
+        <v>0.1035433331423654</v>
       </c>
       <c r="H61">
-        <v>0.6007241187661517</v>
+        <v>0.4101678839380683</v>
       </c>
       <c r="I61">
-        <v>0.003920163332633564</v>
+        <v>0.0202245127205245</v>
       </c>
       <c r="J61">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="62">
@@ -2828,22 +2828,22 @@
         </is>
       </c>
       <c r="E62">
-        <v>0.03298111009750926</v>
+        <v>0.03257860179298078</v>
       </c>
       <c r="F62">
-        <v>0.8893103623821643</v>
+        <v>0.8939504283162119</v>
       </c>
       <c r="G62">
-        <v>0.1009102743199399</v>
+        <v>0.1173319945269462</v>
       </c>
       <c r="H62">
-        <v>0.6195809099859484</v>
+        <v>0.4379563731528685</v>
       </c>
       <c r="I62">
-        <v>-0.06792916422243067</v>
+        <v>-0.08475339273396543</v>
       </c>
       <c r="J62">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="63">
@@ -2859,31 +2859,31 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LYRM7</t>
+          <t>UQCC3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Q5U5X0</t>
+          <t>Q6UW78</t>
         </is>
       </c>
       <c r="E63">
-        <v>0.4685107934884805</v>
+        <v>0.2213684256758377</v>
       </c>
       <c r="F63">
-        <v>0.03659471777428962</v>
+        <v>0.7148206631755274</v>
       </c>
       <c r="G63">
-        <v>0.2574366500216705</v>
+        <v>-0.1321026943711558</v>
       </c>
       <c r="H63">
-        <v>0.3137894358982757</v>
+        <v>0.8046803105940793</v>
       </c>
       <c r="I63">
-        <v>0.21107414346681</v>
+        <v>0.3534711200469935</v>
       </c>
       <c r="J63">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="64">
@@ -2899,31 +2899,31 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UQCC3</t>
+          <t>UQCC1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Q6UW78</t>
+          <t>Q9NVA1</t>
         </is>
       </c>
       <c r="E64">
-        <v>0.1024246168835958</v>
+        <v>0.4270326718148674</v>
       </c>
       <c r="F64">
-        <v>0.8846124255104755</v>
+        <v>0.3189746450530747</v>
       </c>
       <c r="G64">
-        <v>-0.09453587106466088</v>
+        <v>0.1660470408016259</v>
       </c>
       <c r="H64">
-        <v>0.9175937806321551</v>
+        <v>0.7040813100781455</v>
       </c>
       <c r="I64">
-        <v>0.1969604879482567</v>
+        <v>0.2609856310132415</v>
       </c>
       <c r="J64">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="65">
@@ -2939,31 +2939,31 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UQCC1</t>
+          <t>UQCC2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Q9NVA1</t>
+          <t>Q9BRT2</t>
         </is>
       </c>
       <c r="E65">
-        <v>0.3063081932788911</v>
+        <v>0.0794150420650368</v>
       </c>
       <c r="F65">
-        <v>0.5471778676884979</v>
+        <v>0.8623981956182702</v>
       </c>
       <c r="G65">
-        <v>0.1308241918151722</v>
+        <v>-0.100091701155506</v>
       </c>
       <c r="H65">
-        <v>0.8433738017628031</v>
+        <v>0.7680880883681653</v>
       </c>
       <c r="I65">
-        <v>0.1754840014637189</v>
+        <v>0.1795067432205428</v>
       </c>
       <c r="J65">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="66">
@@ -2979,31 +2979,31 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UQCC2</t>
+          <t>LYRM7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Q9BRT2</t>
+          <t>Q5U5X0</t>
         </is>
       </c>
       <c r="E66">
-        <v>0.1021569321826341</v>
+        <v>0.470881579723887</v>
       </c>
       <c r="F66">
-        <v>0.8068531373617325</v>
+        <v>0.009959248039872741</v>
       </c>
       <c r="G66">
-        <v>-0.01848317407188205</v>
+        <v>0.3197937887703084</v>
       </c>
       <c r="H66">
-        <v>0.9789913181077134</v>
+        <v>0.0804716560305694</v>
       </c>
       <c r="I66">
-        <v>0.1206401062545162</v>
+        <v>0.1510877909535786</v>
       </c>
       <c r="J66">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="67">
@@ -3028,22 +3028,22 @@
         </is>
       </c>
       <c r="E67">
-        <v>-0.04502436866906123</v>
+        <v>0.04330995499717005</v>
       </c>
       <c r="F67">
-        <v>0.9387936088753962</v>
+        <v>0.947981308737162</v>
       </c>
       <c r="G67">
-        <v>0.1101014316730833</v>
+        <v>0.03052775659850937</v>
       </c>
       <c r="H67">
-        <v>0.8539066303618239</v>
+        <v>0.9582220998512945</v>
       </c>
       <c r="I67">
-        <v>-0.1551258003421445</v>
+        <v>0.01278219839866068</v>
       </c>
       <c r="J67">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="68">
@@ -3068,22 +3068,22 @@
         </is>
       </c>
       <c r="E68">
-        <v>0.269120075675751</v>
+        <v>0.3450244041030821</v>
       </c>
       <c r="F68">
-        <v>0.4275774890444901</v>
+        <v>0.2099056253245155</v>
       </c>
       <c r="G68">
-        <v>0.07202473193515146</v>
+        <v>0.09990149482414878</v>
       </c>
       <c r="H68">
-        <v>0.886008968740262</v>
+        <v>0.7509156218987526</v>
       </c>
       <c r="I68">
-        <v>0.1970953437405996</v>
+        <v>0.2451229092789333</v>
       </c>
       <c r="J68">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="69">
@@ -3108,22 +3108,22 @@
         </is>
       </c>
       <c r="E69">
-        <v>0.2513558618645426</v>
+        <v>0.4069935271493925</v>
       </c>
       <c r="F69">
-        <v>0.6046669176007717</v>
+        <v>0.3400930713248447</v>
       </c>
       <c r="G69">
-        <v>0.05675445189422845</v>
+        <v>0.1846018505107985</v>
       </c>
       <c r="H69">
-        <v>0.9393020262453196</v>
+        <v>0.6685683692770611</v>
       </c>
       <c r="I69">
-        <v>0.1946014099703142</v>
+        <v>0.222391676638594</v>
       </c>
       <c r="J69">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="70">
@@ -3148,22 +3148,22 @@
         </is>
       </c>
       <c r="E70">
-        <v>0.2975530961495956</v>
+        <v>0.3263047516789044</v>
       </c>
       <c r="F70">
-        <v>0.4285521601923848</v>
+        <v>0.383618499476329</v>
       </c>
       <c r="G70">
-        <v>0.1707549418498004</v>
+        <v>0.1142919493722303</v>
       </c>
       <c r="H70">
-        <v>0.6943267742391495</v>
+        <v>0.7751761883354614</v>
       </c>
       <c r="I70">
-        <v>0.1267981542997951</v>
+        <v>0.2120128023066741</v>
       </c>
       <c r="J70">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="71">
@@ -3179,31 +3179,31 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UQCRC1</t>
+          <t>UQCRFS1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>P31930</t>
+          <t>P47985</t>
         </is>
       </c>
       <c r="E71">
-        <v>0.1430470102194157</v>
+        <v>0.1927358518789823</v>
       </c>
       <c r="F71">
-        <v>0.2704554095891106</v>
+        <v>0.4001085097235457</v>
       </c>
       <c r="G71">
-        <v>0.1054949218964829</v>
+        <v>0.1253797130893197</v>
       </c>
       <c r="H71">
-        <v>0.4405681668773077</v>
+        <v>0.5505437073597776</v>
       </c>
       <c r="I71">
-        <v>0.03755208832293278</v>
+        <v>0.06735613878966262</v>
       </c>
       <c r="J71">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="72">
@@ -3219,31 +3219,31 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UQCRFS1</t>
+          <t>UQCRC1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>P47985</t>
+          <t>P31930</t>
         </is>
       </c>
       <c r="E72">
-        <v>0.1530584312045882</v>
+        <v>0.1543139796980135</v>
       </c>
       <c r="F72">
-        <v>0.5427892475385393</v>
+        <v>0.1626695773597149</v>
       </c>
       <c r="G72">
-        <v>0.1159153370077171</v>
+        <v>0.1019430456431998</v>
       </c>
       <c r="H72">
-        <v>0.656321165885644</v>
+        <v>0.3498140618679545</v>
       </c>
       <c r="I72">
-        <v>0.03714309419687112</v>
+        <v>0.05237093405481374</v>
       </c>
       <c r="J72">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="73">
@@ -3268,22 +3268,22 @@
         </is>
       </c>
       <c r="E73">
-        <v>0.1625266683544133</v>
+        <v>0.2161736036042541</v>
       </c>
       <c r="F73">
-        <v>0.2667931007362479</v>
+        <v>0.0769766677776591</v>
       </c>
       <c r="G73">
-        <v>0.1798557491400921</v>
+        <v>0.2009401941242714</v>
       </c>
       <c r="H73">
-        <v>0.1756438097529532</v>
+        <v>0.07070268896848286</v>
       </c>
       <c r="I73">
-        <v>-0.01732908078567874</v>
+        <v>0.01523340947998264</v>
       </c>
       <c r="J73">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="74">
@@ -3308,22 +3308,22 @@
         </is>
       </c>
       <c r="E74">
-        <v>0.08951995846892657</v>
+        <v>0.112215324519692</v>
       </c>
       <c r="F74">
-        <v>0.7514341292633704</v>
+        <v>0.6714451160810182</v>
       </c>
       <c r="G74">
-        <v>0.151366334222871</v>
+        <v>0.1478789954869342</v>
       </c>
       <c r="H74">
-        <v>0.5598314243013638</v>
+        <v>0.4458820413348849</v>
       </c>
       <c r="I74">
-        <v>-0.06184637575394447</v>
+        <v>-0.03566367096724221</v>
       </c>
       <c r="J74">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="75">
@@ -3348,22 +3348,22 @@
         </is>
       </c>
       <c r="E75">
-        <v>0.04468965875970099</v>
+        <v>0.03104537334322544</v>
       </c>
       <c r="F75">
-        <v>0.8846124255104755</v>
+        <v>0.9283129451380019</v>
       </c>
       <c r="G75">
-        <v>0.1363354440537776</v>
+        <v>0.1552454539838877</v>
       </c>
       <c r="H75">
-        <v>0.6012409972508475</v>
+        <v>0.4537766105897836</v>
       </c>
       <c r="I75">
-        <v>-0.09164578529407663</v>
+        <v>-0.1242000806406622</v>
       </c>
       <c r="J75">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="76">
@@ -3388,22 +3388,22 @@
         </is>
       </c>
       <c r="E76">
-        <v>0.06137943341165908</v>
+        <v>0.05458175284148581</v>
       </c>
       <c r="F76">
-        <v>0.8199349212818225</v>
+        <v>0.8647156544759634</v>
       </c>
       <c r="G76">
-        <v>0.1726094778655991</v>
+        <v>0.2432177323482811</v>
       </c>
       <c r="H76">
-        <v>0.4496107803845932</v>
+        <v>0.1654051552387276</v>
       </c>
       <c r="I76">
-        <v>-0.11123004445394</v>
+        <v>-0.1886359795067953</v>
       </c>
       <c r="J76">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="77">
@@ -3428,22 +3428,22 @@
         </is>
       </c>
       <c r="E77">
-        <v>0.1379827033049672</v>
+        <v>0.1907339173326505</v>
       </c>
       <c r="F77">
-        <v>0.6046669176007717</v>
+        <v>0.477316524715102</v>
       </c>
       <c r="G77">
-        <v>0.2567406736686451</v>
+        <v>0.3913182251437632</v>
       </c>
       <c r="H77">
-        <v>0.2242324953703364</v>
+        <v>0.03373924874402252</v>
       </c>
       <c r="I77">
-        <v>-0.1187579703636779</v>
+        <v>-0.2005843078111127</v>
       </c>
       <c r="J77">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="78">
@@ -3468,22 +3468,22 @@
         </is>
       </c>
       <c r="E78">
-        <v>0.5649018812720001</v>
+        <v>0.6758666923085208</v>
       </c>
       <c r="F78">
-        <v>0.3594383159097958</v>
+        <v>0.1468890482537433</v>
       </c>
       <c r="G78">
-        <v>0.01247833259773046</v>
+        <v>0.05803655263275331</v>
       </c>
       <c r="H78">
-        <v>0.9944877956060161</v>
+        <v>0.9339898943011383</v>
       </c>
       <c r="I78">
-        <v>0.5524235486742697</v>
+        <v>0.6178301396757675</v>
       </c>
       <c r="J78">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="79">
@@ -3508,22 +3508,22 @@
         </is>
       </c>
       <c r="E79">
-        <v>0.14506209320081</v>
+        <v>0.2570753625836666</v>
       </c>
       <c r="F79">
-        <v>0.7220440646753976</v>
+        <v>0.4925760124805018</v>
       </c>
       <c r="G79">
-        <v>-0.106642759519044</v>
+        <v>-0.1020436438912746</v>
       </c>
       <c r="H79">
-        <v>0.8251190730278271</v>
+        <v>0.7845851148134271</v>
       </c>
       <c r="I79">
-        <v>0.251704852719854</v>
+        <v>0.3591190064749412</v>
       </c>
       <c r="J79">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="80">
@@ -3548,22 +3548,22 @@
         </is>
       </c>
       <c r="E80">
-        <v>0.2821177409702642</v>
+        <v>0.234521123030536</v>
       </c>
       <c r="F80">
-        <v>0.3074493357040084</v>
+        <v>0.4452703830767067</v>
       </c>
       <c r="G80">
-        <v>0.03493462643507428</v>
+        <v>-0.03708867162014684</v>
       </c>
       <c r="H80">
-        <v>0.9451515138236694</v>
+        <v>0.9245896421923658</v>
       </c>
       <c r="I80">
-        <v>0.2471831145351899</v>
+        <v>0.2716097946506828</v>
       </c>
       <c r="J80">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="81">
@@ -3579,31 +3579,31 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SCO2</t>
+          <t>COX14</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>O43819</t>
+          <t>Q96I36</t>
         </is>
       </c>
       <c r="E81">
-        <v>0.3208979219084664</v>
+        <v>0.08646149590398622</v>
       </c>
       <c r="F81">
-        <v>0.4285521601923848</v>
+        <v>0.8213511311103187</v>
       </c>
       <c r="G81">
-        <v>0.07519152879558177</v>
+        <v>-0.1372824860833095</v>
       </c>
       <c r="H81">
-        <v>0.9054852194544682</v>
+        <v>0.6084480513543282</v>
       </c>
       <c r="I81">
-        <v>0.2457063931128847</v>
+        <v>0.2237439819872957</v>
       </c>
       <c r="J81">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="82">
@@ -3619,31 +3619,31 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TACO1</t>
+          <t>SCO2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Q9BSH4</t>
+          <t>O43819</t>
         </is>
       </c>
       <c r="E82">
-        <v>0.6605041349810996</v>
+        <v>0.2739060551072718</v>
       </c>
       <c r="F82">
-        <v>0.04785015532067167</v>
+        <v>0.4420612600718281</v>
       </c>
       <c r="G82">
-        <v>0.4265227532500546</v>
+        <v>0.06437559846314045</v>
       </c>
       <c r="H82">
-        <v>0.2399552616239489</v>
+        <v>0.8750787598385064</v>
       </c>
       <c r="I82">
-        <v>0.233981381731045</v>
+        <v>0.2095304566441314</v>
       </c>
       <c r="J82">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="83">
@@ -3659,31 +3659,31 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>COX14</t>
+          <t>TACO1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Q96I36</t>
+          <t>Q9BSH4</t>
         </is>
       </c>
       <c r="E83">
-        <v>0.08365954193065939</v>
+        <v>0.635037423012367</v>
       </c>
       <c r="F83">
-        <v>0.8175103430243885</v>
+        <v>0.02325977117180332</v>
       </c>
       <c r="G83">
-        <v>-0.1122150581669459</v>
+        <v>0.4336309378690117</v>
       </c>
       <c r="H83">
-        <v>0.775906463640316</v>
+        <v>0.1241205403476334</v>
       </c>
       <c r="I83">
-        <v>0.1958746000976053</v>
+        <v>0.2014064851433552</v>
       </c>
       <c r="J83">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="84">
@@ -3699,31 +3699,31 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>COA4</t>
+          <t>COA7</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Q9NYJ1</t>
+          <t>Q96BR5</t>
         </is>
       </c>
       <c r="E84">
-        <v>0.2724930849907068</v>
+        <v>0.4214707603702017</v>
       </c>
       <c r="F84">
-        <v>0.09964874342707419</v>
+        <v>0.2907831006381331</v>
       </c>
       <c r="G84">
-        <v>0.1710965010933521</v>
+        <v>0.2435687914979159</v>
       </c>
       <c r="H84">
-        <v>0.353710817077967</v>
+        <v>0.5198583510674387</v>
       </c>
       <c r="I84">
-        <v>0.1013965838973547</v>
+        <v>0.1779019688722858</v>
       </c>
       <c r="J84">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="85">
@@ -3739,31 +3739,31 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>COX20</t>
+          <t>COX11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Q5RI15</t>
+          <t>Q9Y6N1</t>
         </is>
       </c>
       <c r="E85">
-        <v>0.1914675962177448</v>
+        <v>0.2382917992773805</v>
       </c>
       <c r="F85">
-        <v>0.6222483034929829</v>
+        <v>0.444172121346984</v>
       </c>
       <c r="G85">
-        <v>0.1406878134423764</v>
+        <v>0.09729573232867139</v>
       </c>
       <c r="H85">
-        <v>0.7459837861975588</v>
+        <v>0.7526067393345975</v>
       </c>
       <c r="I85">
-        <v>0.05077978277536843</v>
+        <v>0.1409960669487091</v>
       </c>
       <c r="J85">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="86">
@@ -3788,22 +3788,22 @@
         </is>
       </c>
       <c r="E86">
-        <v>0.1219051669905333</v>
+        <v>0.1760988916743997</v>
       </c>
       <c r="F86">
-        <v>0.7205356014196281</v>
+        <v>0.5607684883387538</v>
       </c>
       <c r="G86">
-        <v>0.07301233092055881</v>
+        <v>0.05918695526621676</v>
       </c>
       <c r="H86">
-        <v>0.8605572538886845</v>
+        <v>0.8569348741491358</v>
       </c>
       <c r="I86">
-        <v>0.04889283606997452</v>
+        <v>0.116911936408183</v>
       </c>
       <c r="J86">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="87">
@@ -3819,31 +3819,31 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>COX11</t>
+          <t>COA4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Q9Y6N1</t>
+          <t>Q9NYJ1</t>
         </is>
       </c>
       <c r="E87">
-        <v>0.1347452676809588</v>
+        <v>0.2991045463310513</v>
       </c>
       <c r="F87">
-        <v>0.6606586958560993</v>
+        <v>0.08211631390777707</v>
       </c>
       <c r="G87">
-        <v>0.09368579895010498</v>
+        <v>0.277644672982575</v>
       </c>
       <c r="H87">
-        <v>0.7905939472157125</v>
+        <v>0.0734757722501303</v>
       </c>
       <c r="I87">
-        <v>0.04105946873085387</v>
+        <v>0.02145987334847632</v>
       </c>
       <c r="J87">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="88">
@@ -3859,31 +3859,31 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>COA3</t>
+          <t>COA6</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Q9Y2R0</t>
+          <t>Q5JTJ3</t>
         </is>
       </c>
       <c r="E88">
-        <v>0.02975939584248977</v>
+        <v>0.1811205360671444</v>
       </c>
       <c r="F88">
-        <v>0.9295786548947834</v>
+        <v>0.429100628828654</v>
       </c>
       <c r="G88">
-        <v>0.03418020248769338</v>
+        <v>0.2014584787548372</v>
       </c>
       <c r="H88">
-        <v>0.9348136826521125</v>
+        <v>0.2818301968840408</v>
       </c>
       <c r="I88">
-        <v>-0.004420806645203612</v>
+        <v>-0.02033794268769284</v>
       </c>
       <c r="J88">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="89">
@@ -3899,31 +3899,31 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SMIM20</t>
+          <t>CMC2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Q8N5G0</t>
+          <t>Q9NRP2</t>
         </is>
       </c>
       <c r="E89">
-        <v>0.2599021184739136</v>
+        <v>0.2177023124505872</v>
       </c>
       <c r="F89">
-        <v>0.627079112561329</v>
+        <v>0.4848450843319864</v>
       </c>
       <c r="G89">
-        <v>0.2887617866970125</v>
+        <v>0.239719437105542</v>
       </c>
       <c r="H89">
-        <v>0.5804950448709141</v>
+        <v>0.3353633181795951</v>
       </c>
       <c r="I89">
-        <v>-0.02885966822309882</v>
+        <v>-0.02201712465495476</v>
       </c>
       <c r="J89">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="90">
@@ -3939,31 +3939,31 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>COA7</t>
+          <t>COX20</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Q96BR5</t>
+          <t>Q5RI15</t>
         </is>
       </c>
       <c r="E90">
-        <v>0.3134634609306861</v>
+        <v>0.2022887703253069</v>
       </c>
       <c r="F90">
-        <v>0.5618300791770688</v>
+        <v>0.5994640619867394</v>
       </c>
       <c r="G90">
-        <v>0.3697632504752288</v>
+        <v>0.2336603458806366</v>
       </c>
       <c r="H90">
-        <v>0.4458464035980284</v>
+        <v>0.427761592468458</v>
       </c>
       <c r="I90">
-        <v>-0.05629978954454273</v>
+        <v>-0.03137157555532966</v>
       </c>
       <c r="J90">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="91">
@@ -3979,31 +3979,31 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>COX17</t>
+          <t>SMIM20</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Q14061</t>
+          <t>Q8N5G0</t>
         </is>
       </c>
       <c r="E91">
-        <v>0.1738209898290037</v>
+        <v>0.3568514688662567</v>
       </c>
       <c r="F91">
-        <v>0.3444315893768999</v>
+        <v>0.4297951899821872</v>
       </c>
       <c r="G91">
-        <v>0.2503015996935112</v>
+        <v>0.4072781410505222</v>
       </c>
       <c r="H91">
-        <v>0.09489903612699155</v>
+        <v>0.2601131055343209</v>
       </c>
       <c r="I91">
-        <v>-0.07648060986450744</v>
+        <v>-0.05042667218426544</v>
       </c>
       <c r="J91">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="92">
@@ -4019,31 +4019,31 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>COA6</t>
+          <t>COX17</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Q5JTJ3</t>
+          <t>Q14061</t>
         </is>
       </c>
       <c r="E92">
-        <v>0.1682191424580139</v>
+        <v>0.1857796324003331</v>
       </c>
       <c r="F92">
-        <v>0.4606234361477539</v>
+        <v>0.2502562559515356</v>
       </c>
       <c r="G92">
-        <v>0.2477769763633866</v>
+        <v>0.2407910364616583</v>
       </c>
       <c r="H92">
-        <v>0.1944497681757021</v>
+        <v>0.06008030714000358</v>
       </c>
       <c r="I92">
-        <v>-0.07955783390537263</v>
+        <v>-0.05501140406132521</v>
       </c>
       <c r="J92">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="93">
@@ -4059,31 +4059,31 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CMC2</t>
+          <t>COA3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Q9NRP2</t>
+          <t>Q9Y2R0</t>
         </is>
       </c>
       <c r="E93">
-        <v>0.1675297587044504</v>
+        <v>-0.02165271181289086</v>
       </c>
       <c r="F93">
-        <v>0.5979927475415191</v>
+        <v>0.9600829859481588</v>
       </c>
       <c r="G93">
-        <v>0.2608104272849587</v>
+        <v>0.03411288114876854</v>
       </c>
       <c r="H93">
-        <v>0.3145049778974639</v>
+        <v>0.9199734354462398</v>
       </c>
       <c r="I93">
-        <v>-0.09328066858050832</v>
+        <v>-0.05576559296165939</v>
       </c>
       <c r="J93">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="94">
@@ -4108,22 +4108,22 @@
         </is>
       </c>
       <c r="E94">
-        <v>0.06373374843520452</v>
+        <v>0.1781986808167737</v>
       </c>
       <c r="F94">
-        <v>0.831070959297066</v>
+        <v>0.5835748770115725</v>
       </c>
       <c r="G94">
-        <v>0.2410470027328309</v>
+        <v>0.2691527704487839</v>
       </c>
       <c r="H94">
-        <v>0.2846167256509129</v>
+        <v>0.2487683982388904</v>
       </c>
       <c r="I94">
-        <v>-0.1773132542976263</v>
+        <v>-0.09095408963201024</v>
       </c>
       <c r="J94">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="95">
@@ -4148,22 +4148,22 @@
         </is>
       </c>
       <c r="E95">
-        <v>-0.1498701963759608</v>
+        <v>-0.1039266020028577</v>
       </c>
       <c r="F95">
-        <v>0.7515426840933505</v>
+        <v>0.823438112056762</v>
       </c>
       <c r="G95">
-        <v>0.2906111686133279</v>
+        <v>0.2854211906157413</v>
       </c>
       <c r="H95">
-        <v>0.4849678543696916</v>
+        <v>0.333624242744445</v>
       </c>
       <c r="I95">
-        <v>-0.4404813649892887</v>
+        <v>-0.3893477926185991</v>
       </c>
       <c r="J95">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="96">
@@ -4179,31 +4179,31 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MT-CO1</t>
+          <t>COX7C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>P00395</t>
+          <t>P15954</t>
         </is>
       </c>
       <c r="E96">
-        <v>0.03553358966770404</v>
+        <v>0.1479094311875819</v>
       </c>
       <c r="F96">
-        <v>0.971627240070525</v>
+        <v>0.7363192419536965</v>
       </c>
       <c r="G96">
-        <v>-0.3182014969527671</v>
+        <v>-0.1489715176432256</v>
       </c>
       <c r="H96">
-        <v>0.6043282669200536</v>
+        <v>0.6652579057362378</v>
       </c>
       <c r="I96">
-        <v>0.3537350866204712</v>
+        <v>0.2968809488308075</v>
       </c>
       <c r="J96">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="97">
@@ -4219,31 +4219,31 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>COX7C</t>
+          <t>MT-CO1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>P15954</t>
+          <t>P00395</t>
         </is>
       </c>
       <c r="E97">
-        <v>0.1501746178112917</v>
+        <v>0.1146271560605818</v>
       </c>
       <c r="F97">
-        <v>0.7640769122769963</v>
+        <v>0.8914797000186788</v>
       </c>
       <c r="G97">
-        <v>-0.09932295170870731</v>
+        <v>-0.1775818611703563</v>
       </c>
       <c r="H97">
-        <v>0.8762069163764493</v>
+        <v>0.772304533010197</v>
       </c>
       <c r="I97">
-        <v>0.249497569519999</v>
+        <v>0.2922090172309382</v>
       </c>
       <c r="J97">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="98">
@@ -4259,31 +4259,31 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>COX7B</t>
+          <t>COX6A2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>P24311</t>
+          <t>Q02221</t>
         </is>
       </c>
       <c r="E98">
-        <v>0.2951327183162178</v>
+        <v>0.0892864523561343</v>
       </c>
       <c r="F98">
-        <v>0.5303230431137477</v>
+        <v>0.9148151219343568</v>
       </c>
       <c r="G98">
-        <v>0.1957062860184493</v>
+        <v>-0.0128568700404692</v>
       </c>
       <c r="H98">
-        <v>0.6988512271292495</v>
+        <v>0.993217584673133</v>
       </c>
       <c r="I98">
-        <v>0.09942643229776849</v>
+        <v>0.1021433223966035</v>
       </c>
       <c r="J98">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="99">
@@ -4299,31 +4299,31 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>COX7A2</t>
+          <t>COX7A1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>P14406</t>
+          <t>P24310</t>
         </is>
       </c>
       <c r="E99">
-        <v>0.3368966045223516</v>
+        <v>0.2122024618479017</v>
       </c>
       <c r="F99">
-        <v>0.2140410772387158</v>
+        <v>0.550942202971208</v>
       </c>
       <c r="G99">
-        <v>0.299233805854783</v>
+        <v>0.1562868957343042</v>
       </c>
       <c r="H99">
-        <v>0.2666221430326463</v>
+        <v>0.6086787459674382</v>
       </c>
       <c r="I99">
-        <v>0.03766279866756861</v>
+        <v>0.05591556611359749</v>
       </c>
       <c r="J99">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="100">
@@ -4339,31 +4339,31 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NDUFA4</t>
+          <t>MT-CO3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>O00483</t>
+          <t>P00414</t>
         </is>
       </c>
       <c r="E100">
-        <v>0.2615362881030379</v>
+        <v>0.2355935109040388</v>
       </c>
       <c r="F100">
-        <v>0.4302326153397392</v>
+        <v>0.6466671522554328</v>
       </c>
       <c r="G100">
-        <v>0.2261994753085332</v>
+        <v>0.194804970125368</v>
       </c>
       <c r="H100">
-        <v>0.5047226728057803</v>
+        <v>0.643939268121138</v>
       </c>
       <c r="I100">
-        <v>0.03533681279450462</v>
+        <v>0.04078854077867078</v>
       </c>
       <c r="J100">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="101">
@@ -4379,31 +4379,31 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>COX6A2</t>
+          <t>COX7A2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Q02221</t>
+          <t>P14406</t>
         </is>
       </c>
       <c r="E101">
-        <v>0.001678676014655878</v>
+        <v>0.2831379503573821</v>
       </c>
       <c r="F101">
-        <v>0.9967734640645376</v>
+        <v>0.2858265424369451</v>
       </c>
       <c r="G101">
-        <v>-0.02871916218393622</v>
+        <v>0.2516912462223893</v>
       </c>
       <c r="H101">
-        <v>0.9860456748518377</v>
+        <v>0.2669626389263727</v>
       </c>
       <c r="I101">
-        <v>0.0303978381985921</v>
+        <v>0.03144670413499284</v>
       </c>
       <c r="J101">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="102">
@@ -4419,31 +4419,31 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>COX7A1</t>
+          <t>NDUFA4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>P24310</t>
+          <t>O00483</t>
         </is>
       </c>
       <c r="E102">
-        <v>0.2233596130934146</v>
+        <v>0.2101645363766167</v>
       </c>
       <c r="F102">
-        <v>0.5353174016375608</v>
+        <v>0.5512002870417179</v>
       </c>
       <c r="G102">
-        <v>0.2059999217732411</v>
+        <v>0.2181476403605096</v>
       </c>
       <c r="H102">
-        <v>0.563571146785104</v>
+        <v>0.4300919180094863</v>
       </c>
       <c r="I102">
-        <v>0.01735969132017345</v>
+        <v>-0.007983103983892903</v>
       </c>
       <c r="J102">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="103">
@@ -4459,31 +4459,31 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MT-CO3</t>
+          <t>COX7B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>P00414</t>
+          <t>P24311</t>
         </is>
       </c>
       <c r="E103">
-        <v>0.2146055870787293</v>
+        <v>0.2114950914548537</v>
       </c>
       <c r="F103">
-        <v>0.703880959843442</v>
+        <v>0.6728893399751842</v>
       </c>
       <c r="G103">
-        <v>0.226516378258836</v>
+        <v>0.2469421970131513</v>
       </c>
       <c r="H103">
-        <v>0.679852804049859</v>
+        <v>0.5180379650985444</v>
       </c>
       <c r="I103">
-        <v>-0.01191079118010663</v>
+        <v>-0.03544710555829766</v>
       </c>
       <c r="J103">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="104">
@@ -4508,22 +4508,22 @@
         </is>
       </c>
       <c r="E104">
-        <v>0.1814917362281854</v>
+        <v>0.162081202915676</v>
       </c>
       <c r="F104">
-        <v>0.4285521601923848</v>
+        <v>0.5067686974486751</v>
       </c>
       <c r="G104">
-        <v>0.2555058880284093</v>
+        <v>0.2525802704100357</v>
       </c>
       <c r="H104">
-        <v>0.1933771658658845</v>
+        <v>0.1510637374688628</v>
       </c>
       <c r="I104">
-        <v>-0.07401415180022397</v>
+        <v>-0.09049906749435976</v>
       </c>
       <c r="J104">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="105">
@@ -4548,22 +4548,22 @@
         </is>
       </c>
       <c r="E105">
-        <v>0.1319026935552543</v>
+        <v>0.1627673014916269</v>
       </c>
       <c r="F105">
-        <v>0.7764628099296441</v>
+        <v>0.7021179587481993</v>
       </c>
       <c r="G105">
-        <v>0.2494273880279838</v>
+        <v>0.2821207133517074</v>
       </c>
       <c r="H105">
-        <v>0.5669330005343736</v>
+        <v>0.3377929535691507</v>
       </c>
       <c r="I105">
-        <v>-0.1175246944727295</v>
+        <v>-0.1193534118600805</v>
       </c>
       <c r="J105">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="106">
@@ -4579,31 +4579,31 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>COX6C</t>
+          <t>COX6B1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>P09669</t>
+          <t>P14854</t>
         </is>
       </c>
       <c r="E106">
-        <v>0.2546260090623349</v>
+        <v>0.118795956378726</v>
       </c>
       <c r="F106">
-        <v>0.6036268124998954</v>
+        <v>0.6250769747785222</v>
       </c>
       <c r="G106">
-        <v>0.3741859885229992</v>
+        <v>0.2866906294758103</v>
       </c>
       <c r="H106">
-        <v>0.3860213374916774</v>
+        <v>0.06190390212672413</v>
       </c>
       <c r="I106">
-        <v>-0.1195599794606643</v>
+        <v>-0.1678946730970843</v>
       </c>
       <c r="J106">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="107">
@@ -4619,31 +4619,31 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>COX6B1</t>
+          <t>COX4I1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>P14854</t>
+          <t>P13073</t>
         </is>
       </c>
       <c r="E107">
-        <v>0.1642322877700408</v>
+        <v>0.06703262590355408</v>
       </c>
       <c r="F107">
-        <v>0.4942548444440714</v>
+        <v>0.7461067099560694</v>
       </c>
       <c r="G107">
-        <v>0.2958836664900737</v>
+        <v>0.2600238553501697</v>
       </c>
       <c r="H107">
-        <v>0.1058453747033006</v>
+        <v>0.03082725984175293</v>
       </c>
       <c r="I107">
-        <v>-0.1316513787200329</v>
+        <v>-0.1929912294466156</v>
       </c>
       <c r="J107">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="108">
@@ -4659,31 +4659,31 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>COX4I1</t>
+          <t>MT-CO2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>P13073</t>
+          <t>P00403</t>
         </is>
       </c>
       <c r="E108">
-        <v>0.0919179753765107</v>
+        <v>0.06995419001365732</v>
       </c>
       <c r="F108">
-        <v>0.6411117946244019</v>
+        <v>0.866383278186972</v>
       </c>
       <c r="G108">
-        <v>0.2474847665562194</v>
+        <v>0.3160838762758971</v>
       </c>
       <c r="H108">
-        <v>0.06866411943061053</v>
+        <v>0.1785004664577841</v>
       </c>
       <c r="I108">
-        <v>-0.1555667911797087</v>
+        <v>-0.2461296862622397</v>
       </c>
       <c r="J108">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="109">
@@ -4699,31 +4699,31 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MT-CO2</t>
+          <t>COX5A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>P00403</t>
+          <t>P20674</t>
         </is>
       </c>
       <c r="E109">
-        <v>0.05306006125645268</v>
+        <v>0.07695294757476745</v>
       </c>
       <c r="F109">
-        <v>0.8985656263419146</v>
+        <v>0.8527272479446132</v>
       </c>
       <c r="G109">
-        <v>0.3033895102563342</v>
+        <v>0.364384615682134</v>
       </c>
       <c r="H109">
-        <v>0.2846167256509129</v>
+        <v>0.1060327807438357</v>
       </c>
       <c r="I109">
-        <v>-0.2503294489998815</v>
+        <v>-0.2874316681073665</v>
       </c>
       <c r="J109">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="110">
@@ -4739,31 +4739,31 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>COX5A</t>
+          <t>COX6C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>P20674</t>
+          <t>P09669</t>
         </is>
       </c>
       <c r="E110">
-        <v>0.0391273416379363</v>
+        <v>0.1438492989952103</v>
       </c>
       <c r="F110">
-        <v>0.9280333228629465</v>
+        <v>0.8354165937087069</v>
       </c>
       <c r="G110">
-        <v>0.2998337456643476</v>
+        <v>0.4404137952711906</v>
       </c>
       <c r="H110">
-        <v>0.2846167256509129</v>
+        <v>0.3056078431301459</v>
       </c>
       <c r="I110">
-        <v>-0.2607064040264113</v>
+        <v>-0.2965644962759804</v>
       </c>
       <c r="J110">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="111">
@@ -4788,22 +4788,22 @@
         </is>
       </c>
       <c r="E111">
-        <v>-0.01130631984843689</v>
+        <v>0.01789795448005194</v>
       </c>
       <c r="F111">
-        <v>0.9887101634047901</v>
+        <v>0.9838842942700481</v>
       </c>
       <c r="G111">
-        <v>0.3882445629059994</v>
+        <v>0.3477295942301808</v>
       </c>
       <c r="H111">
-        <v>0.3775289138592215</v>
+        <v>0.3615318221200493</v>
       </c>
       <c r="I111">
-        <v>-0.3995508827544363</v>
+        <v>-0.3298316397501289</v>
       </c>
       <c r="J111">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="112">
@@ -4828,22 +4828,22 @@
         </is>
       </c>
       <c r="E112">
-        <v>0.2591639714302794</v>
+        <v>0.359738097217857</v>
       </c>
       <c r="F112">
-        <v>0.3948822100752121</v>
+        <v>0.2167664439071577</v>
       </c>
       <c r="G112">
-        <v>0.03093271978699974</v>
+        <v>-0.04387161718202748</v>
       </c>
       <c r="H112">
-        <v>0.9566393026911676</v>
+        <v>0.9199734354462398</v>
       </c>
       <c r="I112">
-        <v>0.2282312516432796</v>
+        <v>0.4036097143998845</v>
       </c>
       <c r="J112">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="113">
@@ -4868,22 +4868,22 @@
         </is>
       </c>
       <c r="E113">
-        <v>0.462049733138354</v>
+        <v>0.5014159988898044</v>
       </c>
       <c r="F113">
-        <v>0.1233196069092226</v>
+        <v>0.06783793776667787</v>
       </c>
       <c r="G113">
-        <v>0.2675391680041201</v>
+        <v>0.251251681366309</v>
       </c>
       <c r="H113">
-        <v>0.4385669173810596</v>
+        <v>0.3923136748529599</v>
       </c>
       <c r="I113">
-        <v>0.1945105651342338</v>
+        <v>0.2501643175234953</v>
       </c>
       <c r="J113">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="114">
@@ -4908,22 +4908,22 @@
         </is>
       </c>
       <c r="E114">
-        <v>0.3073989004417363</v>
+        <v>0.4589218076571271</v>
       </c>
       <c r="F114">
-        <v>0.5081921954057165</v>
+        <v>0.1614212077231257</v>
       </c>
       <c r="G114">
-        <v>0.2314208215629137</v>
+        <v>0.2108441029273003</v>
       </c>
       <c r="H114">
-        <v>0.6381040614428798</v>
+        <v>0.5442291452548023</v>
       </c>
       <c r="I114">
-        <v>0.07597807887882269</v>
+        <v>0.2480777047298268</v>
       </c>
       <c r="J114">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="115">
@@ -4948,22 +4948,22 @@
         </is>
       </c>
       <c r="E115">
-        <v>-0.1881016731427216</v>
+        <v>-0.2188710566699505</v>
       </c>
       <c r="F115">
-        <v>0.6592707591478006</v>
+        <v>0.5709746635871441</v>
       </c>
       <c r="G115">
-        <v>-0.075932648390026</v>
+        <v>0.0667199680686501</v>
       </c>
       <c r="H115">
-        <v>0.8974362361544456</v>
+        <v>0.872162398321992</v>
       </c>
       <c r="I115">
-        <v>-0.1121690247526956</v>
+        <v>-0.2855910247386007</v>
       </c>
       <c r="J115">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="116">
@@ -4979,31 +4979,31 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ATP5MPL</t>
+          <t>ATP5MF</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>P56378</t>
+          <t>P56134</t>
         </is>
       </c>
       <c r="E116">
-        <v>0.2355675174586338</v>
+        <v>0.2876134982681258</v>
       </c>
       <c r="F116">
-        <v>0.5979927475415191</v>
+        <v>0.6433063230626341</v>
       </c>
       <c r="G116">
-        <v>0.003433670615692108</v>
+        <v>0.1113992129118309</v>
       </c>
       <c r="H116">
-        <v>0.9972952269581049</v>
+        <v>0.8607205120813491</v>
       </c>
       <c r="I116">
-        <v>0.2321338468429417</v>
+        <v>0.1762142853562949</v>
       </c>
       <c r="J116">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="117">
@@ -5019,31 +5019,31 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ATP5ME</t>
+          <t>DMAC2L</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>P56385</t>
+          <t>Q99766</t>
         </is>
       </c>
       <c r="E117">
-        <v>0.2179811550125486</v>
+        <v>0.0885200620975688</v>
       </c>
       <c r="F117">
-        <v>0.4248509705899959</v>
+        <v>0.8164965757766455</v>
       </c>
       <c r="G117">
-        <v>0.08534137749449044</v>
+        <v>-0.07804215537430181</v>
       </c>
       <c r="H117">
-        <v>0.8146838151720459</v>
+        <v>0.8002559941225003</v>
       </c>
       <c r="I117">
-        <v>0.1326397775180581</v>
+        <v>0.1665622174718706</v>
       </c>
       <c r="J117">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="118">
@@ -5059,31 +5059,31 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DMAC2L</t>
+          <t>ATP5F1C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Q99766</t>
+          <t>P36542</t>
         </is>
       </c>
       <c r="E118">
-        <v>0.01196508944569707</v>
+        <v>0.3219269620134035</v>
       </c>
       <c r="F118">
-        <v>0.9826070070796277</v>
+        <v>0.1704291195170323</v>
       </c>
       <c r="G118">
-        <v>-0.1043417405444327</v>
+        <v>0.1758056262769649</v>
       </c>
       <c r="H118">
-        <v>0.7616219594992272</v>
+        <v>0.4684368129024939</v>
       </c>
       <c r="I118">
-        <v>0.1163068299901298</v>
+        <v>0.1461213357364386</v>
       </c>
       <c r="J118">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="119">
@@ -5099,31 +5099,31 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ATP5MF</t>
+          <t>ATP5MPL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>P56134</t>
+          <t>P56378</t>
         </is>
       </c>
       <c r="E119">
-        <v>0.1991250516162495</v>
+        <v>0.297789196667761</v>
       </c>
       <c r="F119">
-        <v>0.7573204667869908</v>
+        <v>0.4545275743573051</v>
       </c>
       <c r="G119">
-        <v>0.1125362902246003</v>
+        <v>0.1528574353608612</v>
       </c>
       <c r="H119">
-        <v>0.8944833746618237</v>
+        <v>0.6844401953994765</v>
       </c>
       <c r="I119">
-        <v>0.08658876139164917</v>
+        <v>0.1449317613068999</v>
       </c>
       <c r="J119">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="120">
@@ -5139,31 +5139,31 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ATP5F1B</t>
+          <t>MT-ATP6</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>P06576</t>
+          <t>P00846</t>
         </is>
       </c>
       <c r="E120">
-        <v>0.1216564706018168</v>
+        <v>0.1051667370243692</v>
       </c>
       <c r="F120">
-        <v>0.4285521601923848</v>
+        <v>0.8513438503192678</v>
       </c>
       <c r="G120">
-        <v>0.04827348526366748</v>
+        <v>0.001333881242338464</v>
       </c>
       <c r="H120">
-        <v>0.8146838151720459</v>
+        <v>0.9986383493394465</v>
       </c>
       <c r="I120">
-        <v>0.07338298533814935</v>
+        <v>0.1038328557820307</v>
       </c>
       <c r="J120">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="121">
@@ -5179,31 +5179,31 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ATP5F1C</t>
+          <t>ATP5F1A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>P36542</t>
+          <t>P25705</t>
         </is>
       </c>
       <c r="E121">
-        <v>0.2159082580436582</v>
+        <v>0.1708843263056927</v>
       </c>
       <c r="F121">
-        <v>0.424772528475836</v>
+        <v>0.1114933429604384</v>
       </c>
       <c r="G121">
-        <v>0.1512816082201667</v>
+        <v>0.09329449261563028</v>
       </c>
       <c r="H121">
-        <v>0.6054486704135216</v>
+        <v>0.3960967987300094</v>
       </c>
       <c r="I121">
-        <v>0.06462664982349153</v>
+        <v>0.07758983369006245</v>
       </c>
       <c r="J121">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="122">
@@ -5219,31 +5219,31 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ATP5MG</t>
+          <t>ATP5ME</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>O75964</t>
+          <t>P56385</t>
         </is>
       </c>
       <c r="E122">
-        <v>0.1630121693027853</v>
+        <v>0.2249119803986339</v>
       </c>
       <c r="F122">
-        <v>0.3554843170212468</v>
+        <v>0.3662280948134094</v>
       </c>
       <c r="G122">
-        <v>0.1090463036484408</v>
+        <v>0.1621761739758583</v>
       </c>
       <c r="H122">
-        <v>0.5731922447400792</v>
+        <v>0.4714610826980394</v>
       </c>
       <c r="I122">
-        <v>0.05396586565434447</v>
+        <v>0.06273580642277565</v>
       </c>
       <c r="J122">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="123">
@@ -5259,31 +5259,31 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ATP5F1A</t>
+          <t>ATP5F1B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>P25705</t>
+          <t>P06576</t>
         </is>
       </c>
       <c r="E123">
-        <v>0.1302349943089247</v>
+        <v>0.1241111679001214</v>
       </c>
       <c r="F123">
-        <v>0.322897497758947</v>
+        <v>0.4297951899821872</v>
       </c>
       <c r="G123">
-        <v>0.1218127009957719</v>
+        <v>0.07218839604272276</v>
       </c>
       <c r="H123">
-        <v>0.3241433701360466</v>
+        <v>0.6193261410034274</v>
       </c>
       <c r="I123">
-        <v>0.008422293313152807</v>
+        <v>0.05192277185739869</v>
       </c>
       <c r="J123">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="124">
@@ -5299,31 +5299,31 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ATP5PB</t>
+          <t>ATP5MG</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>P24539</t>
+          <t>O75964</t>
         </is>
       </c>
       <c r="E124">
-        <v>0.1570266227014798</v>
+        <v>0.1923080464530962</v>
       </c>
       <c r="F124">
-        <v>0.350426217365032</v>
+        <v>0.2099056253245155</v>
       </c>
       <c r="G124">
-        <v>0.1526184928612153</v>
+        <v>0.156040026690512</v>
       </c>
       <c r="H124">
-        <v>0.3231223321824719</v>
+        <v>0.2644325130675522</v>
       </c>
       <c r="I124">
-        <v>0.004408129840264507</v>
+        <v>0.0362680197625842</v>
       </c>
       <c r="J124">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="125">
@@ -5339,31 +5339,31 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ATP5PD</t>
+          <t>ATP5PB</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>O75947</t>
+          <t>P24539</t>
         </is>
       </c>
       <c r="E125">
-        <v>0.1137222027263469</v>
+        <v>0.2129094172032389</v>
       </c>
       <c r="F125">
-        <v>0.5516921313007371</v>
+        <v>0.1316073214050267</v>
       </c>
       <c r="G125">
-        <v>0.1189463250518124</v>
+        <v>0.20776251809502</v>
       </c>
       <c r="H125">
-        <v>0.5117582702622031</v>
+        <v>0.09739494435688292</v>
       </c>
       <c r="I125">
-        <v>-0.00522412232546543</v>
+        <v>0.005146899108218861</v>
       </c>
       <c r="J125">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="126">
@@ -5388,22 +5388,22 @@
         </is>
       </c>
       <c r="E126">
-        <v>0.0489122418746426</v>
+        <v>0.04941186781489648</v>
       </c>
       <c r="F126">
-        <v>0.8805508448520581</v>
+        <v>0.8839201002236267</v>
       </c>
       <c r="G126">
-        <v>0.06475613145995496</v>
+        <v>0.09270964201618881</v>
       </c>
       <c r="H126">
-        <v>0.8577606328780856</v>
+        <v>0.6967449972698464</v>
       </c>
       <c r="I126">
-        <v>-0.01584388958531235</v>
+        <v>-0.04329777420129233</v>
       </c>
       <c r="J126">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="127">
@@ -5419,31 +5419,31 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MT-ATP6</t>
+          <t>ATP5PD</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>P00846</t>
+          <t>O75947</t>
         </is>
       </c>
       <c r="E127">
-        <v>0.01113189645237256</v>
+        <v>0.1101845765699139</v>
       </c>
       <c r="F127">
-        <v>0.986838960875012</v>
+        <v>0.5223933325781615</v>
       </c>
       <c r="G127">
-        <v>0.02796346010455864</v>
+        <v>0.1600749636112226</v>
       </c>
       <c r="H127">
-        <v>0.9697477471237287</v>
+        <v>0.1978087442279915</v>
       </c>
       <c r="I127">
-        <v>-0.01683156365218608</v>
+        <v>-0.04989038704130877</v>
       </c>
       <c r="J127">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="128">
@@ -5459,31 +5459,31 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ATP5PO</t>
+          <t>ATP5IF1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>P48047</t>
+          <t>Q9UII2</t>
         </is>
       </c>
       <c r="E128">
-        <v>0.1066246295251432</v>
+        <v>0.1570603488070645</v>
       </c>
       <c r="F128">
-        <v>0.5516921313007371</v>
+        <v>0.7199556250412755</v>
       </c>
       <c r="G128">
-        <v>0.1516925495990442</v>
+        <v>0.2224975363419546</v>
       </c>
       <c r="H128">
-        <v>0.3089332217657619</v>
+        <v>0.4807053760924017</v>
       </c>
       <c r="I128">
-        <v>-0.04506792007390104</v>
+        <v>-0.06543718753489003</v>
       </c>
       <c r="J128">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="129">
@@ -5508,22 +5508,22 @@
         </is>
       </c>
       <c r="E129">
-        <v>0.03957275343870492</v>
+        <v>0.02361677332596201</v>
       </c>
       <c r="F129">
-        <v>0.8621200159638345</v>
+        <v>0.9227419425236174</v>
       </c>
       <c r="G129">
-        <v>0.1128426899208144</v>
+        <v>0.1056520817159026</v>
       </c>
       <c r="H129">
-        <v>0.5569767112410837</v>
+        <v>0.4824377324635152</v>
       </c>
       <c r="I129">
-        <v>-0.07326993648210944</v>
+        <v>-0.08203530838994055</v>
       </c>
       <c r="J129">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="130">
@@ -5539,31 +5539,31 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ATP5F1D</t>
+          <t>ATP5PO</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>P30049</t>
+          <t>P48047</t>
         </is>
       </c>
       <c r="E130">
-        <v>0.1524248647627147</v>
+        <v>0.05523125132295448</v>
       </c>
       <c r="F130">
-        <v>0.5674207352113838</v>
+        <v>0.7936115100646932</v>
       </c>
       <c r="G130">
-        <v>0.2337048366125174</v>
+        <v>0.1620004540657618</v>
       </c>
       <c r="H130">
-        <v>0.2846167256509129</v>
+        <v>0.2047588924194146</v>
       </c>
       <c r="I130">
-        <v>-0.08127997184980273</v>
+        <v>-0.1067692027428073</v>
       </c>
       <c r="J130">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="131">
@@ -5579,31 +5579,31 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ATP5IF1</t>
+          <t>ATP5F1D</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Q9UII2</t>
+          <t>P30049</t>
         </is>
       </c>
       <c r="E131">
-        <v>0.1747519036020115</v>
+        <v>0.1661408489221188</v>
       </c>
       <c r="F131">
-        <v>0.6656713393122349</v>
+        <v>0.509695716566451</v>
       </c>
       <c r="G131">
-        <v>0.2985881630664728</v>
+        <v>0.2813828426530662</v>
       </c>
       <c r="H131">
-        <v>0.3891812313958723</v>
+        <v>0.112959711663197</v>
       </c>
       <c r="I131">
-        <v>-0.1238362594644613</v>
+        <v>-0.1152419937309475</v>
       </c>
       <c r="J131">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
       </c>
     </row>
     <row r="132">
@@ -5628,22 +5628,102 @@
         </is>
       </c>
       <c r="E132">
-        <v>-0.0154473390972214</v>
+        <v>0.03658299463171133</v>
       </c>
       <c r="F132">
-        <v>0.9708555534965511</v>
+        <v>0.9148151219343568</v>
       </c>
       <c r="G132">
-        <v>0.1901815133820683</v>
+        <v>0.2126539939544934</v>
       </c>
       <c r="H132">
-        <v>0.4127459195617104</v>
+        <v>0.2789976752826632</v>
       </c>
       <c r="I132">
-        <v>-0.2056288524792897</v>
+        <v>-0.176070999322782</v>
       </c>
       <c r="J132">
-        <v>0.9999092528331825</v>
+        <v>0.998316285899166</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>CYCS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>P99999</t>
+        </is>
+      </c>
+      <c r="E133">
+        <v>0.3691213551874419</v>
+      </c>
+      <c r="F133">
+        <v>0.2858265424369451</v>
+      </c>
+      <c r="G133">
+        <v>0.2127680215348633</v>
+      </c>
+      <c r="H133">
+        <v>0.5198583510674387</v>
+      </c>
+      <c r="I133">
+        <v>0.1563533336525786</v>
+      </c>
+      <c r="J133">
+        <v>0.998316285899166</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>HCCS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>P53701</t>
+        </is>
+      </c>
+      <c r="E134">
+        <v>0.3365017813696589</v>
+      </c>
+      <c r="F134">
+        <v>0.02744249880533136</v>
+      </c>
+      <c r="G134">
+        <v>0.395436147680492</v>
+      </c>
+      <c r="H134">
+        <v>0.00363100606210797</v>
+      </c>
+      <c r="I134">
+        <v>-0.05893436631083304</v>
+      </c>
+      <c r="J134">
+        <v>0.998316285899166</v>
       </c>
     </row>
   </sheetData>
